--- a/data/sars/keys/area_key_atlantic_final.xlsx
+++ b/data/sars/keys/area_key_atlantic_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/keys/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD26014A-69A5-4C49-990D-C74665C4CC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4068AEB5-3834-6F43-A83D-E25DC4C201B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44640" yWindow="1460" windowWidth="28040" windowHeight="17440" xr2:uid="{9139CB3F-BC9E-A548-9F2C-BB82AE123E2F}"/>
+    <workbookView xWindow="6620" yWindow="1200" windowWidth="28040" windowHeight="17440" xr2:uid="{9139CB3F-BC9E-A548-9F2C-BB82AE123E2F}"/>
   </bookViews>
   <sheets>
     <sheet name="area_key_atlantic_final" sheetId="1" r:id="rId1"/>
@@ -5793,7 +5793,7 @@
         <v>14</v>
       </c>
       <c r="C296" t="s">
-        <v>14</v>
+        <v>237</v>
       </c>
       <c r="D296" t="s">
         <v>248</v>

--- a/data/sars/keys/area_key_atlantic_final.xlsx
+++ b/data/sars/keys/area_key_atlantic_final.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/keys/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4068AEB5-3834-6F43-A83D-E25DC4C201B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6421B73A-AEBC-804A-8B76-2BFFA3990FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6620" yWindow="1200" windowWidth="28040" windowHeight="17440" xr2:uid="{9139CB3F-BC9E-A548-9F2C-BB82AE123E2F}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="area_key_atlantic_final" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">area_key_atlantic_final!$A$1:$D$338</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">area_key_atlantic_final!$A$1:$D$341</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="253">
   <si>
     <t>comm_name</t>
   </si>
@@ -779,6 +779,9 @@
   </si>
   <si>
     <t>Northern Gulf of Mexico Continental Shelf outer</t>
+  </si>
+  <si>
+    <t>Tamanend's bottlenose dolphin</t>
   </si>
 </sst>
 </file>
@@ -1647,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{401FE460-E684-1845-B4A4-30BCCC5E1D62}">
-  <dimension ref="A1:D338"/>
+  <dimension ref="A1:D341"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
@@ -6361,13 +6364,13 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B337" t="s">
-        <v>14</v>
+        <v>170</v>
       </c>
       <c r="C337" t="s">
-        <v>14</v>
+        <v>171</v>
       </c>
       <c r="D337" t="s">
         <v>248</v>
@@ -6375,22 +6378,64 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
+        <v>252</v>
+      </c>
+      <c r="B338" t="s">
+        <v>172</v>
+      </c>
+      <c r="C338" t="s">
+        <v>173</v>
+      </c>
+      <c r="D338" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A339" t="s">
+        <v>252</v>
+      </c>
+      <c r="B339" t="s">
+        <v>178</v>
+      </c>
+      <c r="C339" t="s">
+        <v>179</v>
+      </c>
+      <c r="D339" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A340" t="s">
+        <v>245</v>
+      </c>
+      <c r="B340" t="s">
+        <v>14</v>
+      </c>
+      <c r="C340" t="s">
+        <v>14</v>
+      </c>
+      <c r="D340" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A341" t="s">
         <v>246</v>
       </c>
-      <c r="B338" t="s">
-        <v>14</v>
-      </c>
-      <c r="C338" t="s">
-        <v>14</v>
-      </c>
-      <c r="D338" t="s">
+      <c r="B341" t="s">
+        <v>14</v>
+      </c>
+      <c r="C341" t="s">
+        <v>14</v>
+      </c>
+      <c r="D341" t="s">
         <v>248</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D338" xr:uid="{401FE460-E684-1845-B4A4-30BCCC5E1D62}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D338">
-      <sortCondition ref="A1:A338"/>
+  <autoFilter ref="A1:D341" xr:uid="{401FE460-E684-1845-B4A4-30BCCC5E1D62}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D341">
+      <sortCondition ref="A1:A341"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
